--- a/imagegen-stack/tests/task_eval/eval_sheet.xlsx
+++ b/imagegen-stack/tests/task_eval/eval_sheet.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eval 6 tac vu" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tong hop" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,64 +27,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00141B1A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="0057635F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="007A5AA8"/>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B5601F"/>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001E6FA6"/>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B0322A"/>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="005D8A1F"/>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000B6E63"/>
-      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -92,12 +43,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00141B1A"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF1EF"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+        <bgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,16 +70,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DEE3E0"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00DEE3E0"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00DEE3E0"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DEE3E0"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
   </borders>
@@ -129,38 +88,36 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -247,7 +204,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -272,7 +229,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -297,7 +254,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -322,7 +279,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -347,7 +304,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -369,35 +326,35 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -422,7 +379,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -447,7 +404,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -472,7 +429,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -494,17 +451,42 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -522,14 +504,14 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -547,14 +529,14 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -572,14 +554,14 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -597,14 +579,14 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -622,14 +604,14 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -647,14 +629,14 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -672,14 +654,14 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -697,14 +679,14 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -722,14 +704,39 @@
       <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -747,14 +754,14 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -772,14 +779,14 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -797,39 +804,14 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -847,14 +829,39 @@
       <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -872,14 +879,14 @@
       <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -897,14 +904,14 @@
       <row>33</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -922,14 +929,14 @@
       <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -947,14 +954,14 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -972,14 +979,464 @@
       <row>36</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="857250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1282,16 +1739,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>STT</t>
@@ -1312,569 +1773,2050 @@
           <t>Ảnh</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Preserve</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh ảnh từ text  (5 case)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="86" customHeight="1">
+          <t>T2I — Sinh ảnh từ mô tả text  (7 case)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="67.5" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>T2I
-t2i_01</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>T2I — Sinh ảnh từ mô tả text
+(t2i_01)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Chân dung cận nửa người một cô gái Việt Nam khoảng 25 tuổi mặc áo dài đỏ, tóc đen dài, đứng trước bức tường vàng cũ, ánh sáng tự nhiên từ cửa sổ bên trái, ảnh chụp chân thực, chi tiết cao</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="86" customHeight="1">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="67.5" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>T2I
-t2i_02</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>T2I — Sinh ảnh từ mô tả text
+(t2i_02)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Ảnh sản phẩm: một chai nước mắm thủy tinh trong suốt, nhãn giấy màu nâu, đặt trên bàn gỗ mộc, nền trắng studio, ánh sáng mềm, bóng đổ nhẹ, chụp chân thực</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="86" customHeight="1">
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="67.5" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>T2I
-t2i_03</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>T2I — Sinh ảnh từ mô tả text
+(t2i_03)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Ruộng bậc thang Sa Pa mùa lúa chín vàng, sáng sớm có mây trắng bồng bềnh phía dưới thung lũng, một căn nhà sàn nhỏ bên sườn đồi, ảnh phong cảnh chân thực, góc rộng</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="86" customHeight="1">
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="67.5" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>T2I
-t2i_04</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>T2I — Sinh ảnh từ mô tả text
+(t2i_04)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Quán cà phê vỉa hè Sài Gòn buổi sáng: đúng ba chiếc ghế nhựa màu đỏ và một chiếc bàn nhựa thấp màu xanh, vỉa hè lát gạch, phía sau là bức tường có cửa sắt xanh, không có người, ảnh chụp chân thực</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="86" customHeight="1">
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="67.5" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>T2I
-t2i_05</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>T2I — Sinh ảnh từ mô tả text
+(t2i_05)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Một con mèo mướp xám ngồi trên yên chiếc xe máy Honda cũ màu xanh đậu trong con hẻm nhỏ Hà Nội, tường gạch loang lổ, ánh nắng chiều xiên, ảnh chân thực, chi tiết cao</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Local Edit  (5 case)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="86" customHeight="1">
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="67.5" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>T2I — Sinh ảnh từ mô tả text
+(t2i_06)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Chợ nổi Cái Răng buổi sáng: một chiếc xuồng ba lá chở đầy xoài vàng, một người phụ nữ đội nón lá đang chèo, vài xuồng khác phía xa, ánh nắng sớm, ảnh chụp chân thực, chi tiết cao</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>quả trông giống cam/quýt hơn là xoài (hình tròn thay vì bầu dục); nội dung còn lại (xuồng, nón lá, cảnh chợ nổi) đúng</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="67.5" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>LocalEdit
-loc_01</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Change the color of her ao dai from red to royal blue. Keep her face, hair, pose, the wall and the lighting exactly the same.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="86" customHeight="1">
-      <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>LocalEdit
-loc_02</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Remove the cat completely. The motorbike seat where it was sitting should look natural and empty. Keep everything else exactly the same.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="86" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>T2I — Sinh ảnh từ mô tả text
+(t2i_07)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Bãi biển Mỹ Khê Đà Nẵng lúc hoàng hôn: đúng hai chiếc ghế bố màu trắng đặt cạnh một cây dù màu nâu rơm, sóng biển nhẹ, trời cam hồng, không có người, ảnh chụp chân thực</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)  (9 case)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="67.5" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>LocalEdit
-loc_03</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Add one glass of Vietnamese iced milk coffee on the blue table. Keep the three red chairs, the table, and the background exactly the same.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="86" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_01)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Change the color of her ao dai from red to royal blue. Keep her face, hair, pose, the wall and the lighting exactly the same.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="67.5" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>LocalEdit
-loc_04</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Change the bottle's paper label from brown to dark green. Keep the bottle shape, the liquid, the wooden table and the white background exactly the same.</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="86" customHeight="1">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_02)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Remove the cat completely. The motorbike seat where it was sitting should look natural and empty. Keep everything else exactly the same.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="67.5" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>LocalEdit
-loc_05</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_03)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Add one glass of Vietnamese iced milk coffee on the blue table. Keep the three red chairs, the table, and the background exactly the same.</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>tự thêm 1 ghế: 3→4 ghế thay vì giữ nguyên 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="67.5" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_04)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Change the bottle's paper label from brown to dark green. Keep the bottle shape, the liquid, the wooden table and the white background exactly the same.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="67.5" customHeight="1">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_05)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Replace the small stilt house with a large old tree. Keep the terraces, the clouds and the lighting exactly the same.</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Global Edit  (5 case)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="86" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>GlobalEdit
-glo_01</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="67.5" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_06)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Change the color of the woman's conical hat (non la) to bright yellow. Keep the boat, the mangoes, the other boats and the lighting exactly the same.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="67.5" customHeight="1">
+      <c r="A17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_07)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Add one red beach ball on the sand between the two chairs. Keep the two white chairs, the umbrella and the sunset sky exactly the same.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="67.5" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_08)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Remove the clouds completely, leaving a clear sky. Keep the terraces, the stilt house and the lighting exactly the same.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="67.5" customHeight="1">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>LocalEdit — Sửa cục bộ (đổi màu, thêm/xoá vật)
+(loc_09)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Change the umbrella color from straw/tan to bright red. Keep the two chairs, the sand and the sunset sky exactly the same.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)  (9 case)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="67.5" customHeight="1">
+      <c r="A21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_01)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Change the season: the terraces are now flooded with water during the planting season, reflecting the sky like mirrors. Keep the same composition and viewpoint.</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="86" customHeight="1">
-      <c r="A16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>GlobalEdit
-glo_02</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="67.5" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_02)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Make it night time with warm neon shop lights and wet pavement after rain. Keep the same chairs, table and composition.</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="86" customHeight="1">
-      <c r="A17" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>GlobalEdit
-glo_03</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>đúng chỉ dẫn đêm+neon+ướt, nhưng 3→4 ghế</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="67.5" customHeight="1">
+      <c r="A23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_03)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Convert to a black and white film photograph with fine grain and soft contrast. Keep the person, pose and composition identical.</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="86" customHeight="1">
-      <c r="A18" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>GlobalEdit
-glo_04</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="67.5" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_04)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Turn the whole image into a watercolor painting with soft washes and visible paper texture. Keep the cat, the motorbike and the alley composition.</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="86" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>GlobalEdit
-glo_05</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="67.5" customHeight="1">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_05)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Change the color grading to warm golden-hour tones with soft amber light. Keep the bottle, the table and the framing exactly the same.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Structure Edit  (5 case)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="86" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>StructureEdit
-str_01</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="67.5" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_06)</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Change the time to a foggy early dawn with soft blue-grey light. Keep the same boat, mangoes and composition.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="67.5" customHeight="1">
+      <c r="A27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_07)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Turn the whole image into an oil painting style with visible brush strokes. Keep the two chairs, the umbrella and the composition.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="67.5" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_08)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Make it a rainy scene with wet reflections on the ground and visible rain streaks. Keep the cat, the motorbike and the alley composition.</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="67.5" customHeight="1">
+      <c r="A29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>GlobalEdit — Sửa toàn cục (mùa, ngày→đêm, phong cách)
+(glo_09)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Convert to a black and white documentary photo style with high contrast. Keep the boat, the woman and the mangoes.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình  (9 case)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+    </row>
+    <row r="31" ht="67.5" customHeight="1">
+      <c r="A31" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_01)</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>She turns her head to look to her left, in profile. Keep her face identity, her ao dai, the wall and the lighting the same.</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="86" customHeight="1">
-      <c r="A22" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>StructureEdit
-str_02</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>quay đầu đúng, danh tính khó xác nhận chắc chắn từ profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="67.5" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_02)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>The cat stands up on all four legs and stretches its back. Keep the same cat, the same motorbike and the same alley.</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="86" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>StructureEdit
-str_03</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="67.5" customHeight="1">
+      <c r="A33" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_03)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>There are now exactly five red plastic chairs around the table instead of three. Keep the same chairs style, table and background.</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="86" customHeight="1">
-      <c r="A24" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>StructureEdit
-str_04</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>mục tiêu 5 ghế, ra 4 ghế — KHÔNG đạt, cũng là lỗi đếm lặp lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="67.5" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_04)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Change the camera to a top-down view looking straight down at the bottle on the table. Keep the same bottle, table and white background.</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="86" customHeight="1">
-      <c r="A25" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>StructureEdit
-str_05</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>góc máy từ-trên-xuống THÀNH CÔNG (khác với test riêng lẻ trước đó thất bại) nhưng danh tính chai khó xác nhận từ góc này</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="67.5" customHeight="1">
+      <c r="A35" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_05)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Zoom out to a full-body shot: she is standing, and we see her whole ao dai down to her feet. Keep her identity, outfit, the wall and lighting.</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Ref Gen  (5 case)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="86" customHeight="1">
-      <c r="A27" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>RefGen
-ref_01</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>mở rộng khung hình một phần, chưa rõ đã thấy hết chân</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="67.5" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_06)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>There are now exactly two red plastic chairs around the table instead of three. Keep the same chair style, table and background.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>mục tiêu 2 ghế, ra 4 ghế - lặp lại lỗi đếm giống str_03/loc_03/glo_02 (mô hình có xu hướng vẽ lại số ghế mặc định thay vì làm đúng yêu cầu đếm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="67.5" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_07)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Change the camera to a low angle looking slightly up at the boat. Keep the same boat, mangoes and the woman.</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>góc máy KHÔNG đổi so với ảnh nền, vẫn là góc ngang bình thường, không phải góc thấp hướng lên như yêu cầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="67.5" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_08)</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Zoom in to a close-up of just the two chairs and the umbrella, cropping out the wide sea view. Keep the same chairs and umbrella style.</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>không zoom/crop, khung hình giữ nguyên toàn cảnh như ảnh gốc, chưa cắt riêng 2 ghế+dù như yêu cầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="67.5" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>StructureEdit — Đổi tư thế / góc máy / khung hình
+(str_09)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Rotate the camera to a three-quarter side angle instead of straight-on. Keep the same bottle, table and background.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>góc máy vẫn thẳng (straight-on), KHÔNG đổi sang góc 3/4 nghiêng như yêu cầu</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh  (8 case)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+    </row>
+    <row r="41" ht="67.5" customHeight="1">
+      <c r="A41" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh
+(ref_01)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Generate a new photo of this exact same bottle placed on white sand at a tropical beach at sunset, with the sea in the background. Keep the bottle and its label identical.</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="86" customHeight="1">
-      <c r="A28" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>RefGen
-ref_02</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42" ht="67.5" customHeight="1">
+      <c r="A42" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh
+(ref_02)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Generate a new photo of this same woman, same face and same ao dai, walking through a busy Vietnamese wet market holding a basket.</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="86" customHeight="1">
-      <c r="A29" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>RefGen
-ref_03</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="67.5" customHeight="1">
+      <c r="A43" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh
+(ref_03)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Generate a new photo of this same cat, same fur pattern, lying on a grey sofa in a modern living room.</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="86" customHeight="1">
-      <c r="A30" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>RefGen
-ref_04</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44" ht="67.5" customHeight="1">
+      <c r="A44" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh
+(ref_04)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Generate a new landscape with the same terraced composition and viewpoint, but as sand dunes in a desert at sunset.</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n"/>
-    </row>
-    <row r="31" ht="86" customHeight="1">
-      <c r="A31" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>RefGen
-ref_05</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="67.5" customHeight="1">
+      <c r="A45" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh
+(ref_05)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Generate a new photo in the same photographic style and color palette, but showing a Hoi An old-town street at night with hanging silk lanterns.</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Multi-Ref  (5 case)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="86" customHeight="1">
-      <c r="A33" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>MultiRef
-mref_01</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="67.5" customHeight="1">
+      <c r="A46" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh
+(ref_06)</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Generate a new photo of this exact same boat with the same mangoes, docked at a wooden pier in the evening with string lights. Keep the boat and mango color identical.</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="67.5" customHeight="1">
+      <c r="A47" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh
+(ref_07)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Generate a new photo of these same two white chairs and umbrella, but set up in a green garden instead of a beach. Keep the chairs and umbrella identical.</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48" ht="67.5" customHeight="1">
+      <c r="A48" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>RefGen — Giữ chủ thể, đổi bối cảnh
+(ref_08)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Generate a new photo of this same cat, same fur pattern, sitting on a wooden windowsill looking outside at rain.</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>màu/vằn lông mèo hoàn toàn khác bản gốc (xám trơn → nâu vàng có sọc), không giữ được danh tính mèo</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh  (8 case)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+    </row>
+    <row r="50" ht="67.5" customHeight="1">
+      <c r="A50" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh
+(mref_01)</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Place the woman from image 1 standing in the terraced rice field landscape of image 2, in the foreground. Keep her face, hair and ao dai exactly as in image 1, and match the morning light of image 2.</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="86" customHeight="1">
-      <c r="A34" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>MultiRef
-mref_02</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="67.5" customHeight="1">
+      <c r="A51" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh
+(mref_02)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Place the bottle from image 1 on the blue table in the cafe scene of image 2. Keep the bottle and label identical, and keep the three red chairs of image 2.</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n"/>
-    </row>
-    <row r="35" ht="86" customHeight="1">
-      <c r="A35" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>MultiRef
-mref_03</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>chai đúng 100% nhưng 3→4 ghế (lại lỗi đếm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="67.5" customHeight="1">
+      <c r="A52" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh
+(mref_03)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Place the cat from image 1 sitting on the edge of a rice terrace in the landscape of image 2. Keep the same cat fur pattern.</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n"/>
-    </row>
-    <row r="36" ht="86" customHeight="1">
-      <c r="A36" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>MultiRef
-mref_04</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="67.5" customHeight="1">
+      <c r="A53" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh
+(mref_04)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>The woman from image 1 is holding the cat from image 2 in her arms, in the alley scene of image 2. Keep both the woman's face and the cat's fur pattern identical.</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n"/>
-    </row>
-    <row r="37" ht="86" customHeight="1">
-      <c r="A37" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>MultiRef
-mref_05</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="67.5" customHeight="1">
+      <c r="A54" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh
+(mref_05)</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>The woman from image 1 is holding the bottle from image 2 in her hand, presenting it to the camera, in front of the same yellow wall. Keep her face and the bottle label identical.</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n"/>
+      <c r="D54" s="3" t="n"/>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="67.5" customHeight="1">
+      <c r="A55" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh
+(mref_06)</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Place the fruit boat from image 1 floating near the shore in the beach scene of image 2. Keep the boat and mangoes identical, and keep the two white chairs of image 2.</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>thuyền thay thế vị trí 1 trong 2 ghế thay vì đặt thêm cạnh cả hai ghế, chỉ còn 1 ghế</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="67.5" customHeight="1">
+      <c r="A56" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh
+(mref_07)</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Place the cat from image 1 sitting inside the fruit boat from image 2. Keep the same cat fur pattern and the same boat and mangoes.</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="67.5" customHeight="1">
+      <c r="A57" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>MultiRef — Ghép chủ thể từ 2 ảnh
+(mref_08)</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>The woman from image 1 is sitting on one of the two white beach chairs from image 2, facing the sunset. Keep her face and ao dai identical, and keep both chairs and the umbrella of image 2.</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Tác vụ</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Instruction</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Preserve</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>T2I</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>92.9%</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>LocalEdit</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>GlobalEdit</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>94.4%</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>StructureEdit</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>RefGen</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>MultiRef</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>93.8%</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>81.2%</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Tổng</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>